--- a/backtest_runs/20260410_193731/by_symbol/DWAE/DWAE.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/DWAE/DWAE.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
         <v>-9999.699999999992</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>90000.3</v>
@@ -906,10 +906,10 @@
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>96842.2</v>
@@ -1047,7 +1047,7 @@
         <v>-1947.310000000005</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>94894.88999999998</v>
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="I15" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>94894.88999999998</v>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>94894.88999999998</v>
@@ -1277,7 +1277,7 @@
         <v>-9052.359999999993</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>88210.87999999999</v>
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>88210.87999999999</v>
@@ -1458,10 +1458,10 @@
         </is>
       </c>
       <c r="I22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>88210.87999999999</v>
@@ -1553,7 +1553,7 @@
         <v>-3631.470000000007</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>84579.40999999999</v>
